--- a/AAII_Financials/Quarterly/IVZ_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/IVZ_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="92">
   <si>
     <t>IVZ</t>
   </si>
@@ -656,543 +656,556 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1825600</v>
+      </c>
+      <c r="E8" s="3">
         <v>1744500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1692000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1640400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1515500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1529200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1593000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1515400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1483300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1475300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1413400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1442000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1442800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1418200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1443400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1445700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1530400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1629400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1763400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1750000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1721400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1659700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1630100</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1497600</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1419000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1598900</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1742800</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1720600</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1439400</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1214600</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>1255900</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>1341800</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>1360600</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>1355800</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>1375600</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>1337700</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>1254400</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>1192600</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>1194700</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>1201600</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1283100</v>
+      </c>
+      <c r="E9" s="3">
         <v>1218700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1166000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1189100</v>
       </c>
-      <c r="G9" s="3">
-        <v>1112400</v>
-      </c>
       <c r="H9" s="3">
+        <v>1104400</v>
+      </c>
+      <c r="I9" s="3">
         <v>1087500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1111700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1096400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1064100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1094300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1044000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1037800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1050900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1028400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>447300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>451300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>475000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>512600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>540500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>546400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>539600</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>522800</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>507700</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>480800</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>444000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>515100</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>528100</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>545100</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>451800</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>368000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>372200</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>408000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>408900</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>419100</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>390900</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>380400</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>365900</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>349300</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>349500</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>362100</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>542500</v>
+      </c>
+      <c r="E10" s="3">
         <v>525800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>526000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>451300</v>
       </c>
-      <c r="G10" s="3">
-        <v>403100</v>
-      </c>
       <c r="H10" s="3">
+        <v>411100</v>
+      </c>
+      <c r="I10" s="3">
         <v>441700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>481300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>419000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>419200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>381000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>369400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>404200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>391900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>389800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>996100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>994400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1055400</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1116800</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1222900</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1203600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1181800</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1136900</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1122400</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1016800</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>975000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1083800</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1214700</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1175500</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>987600</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>846600</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>883700</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>933800</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>951700</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>936700</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>984700</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>957300</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>888500</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>843300</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>845200</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>839500</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1235,8 +1248,9 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1357,8 +1371,11 @@
       <c r="AP12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1479,112 +1496,115 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>70700</v>
+      </c>
+      <c r="E14" s="3">
         <v>74700</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>1726800</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>19000</v>
       </c>
-      <c r="G14" s="3">
-        <v>50500</v>
-      </c>
       <c r="H14" s="3">
+        <v>58500</v>
+      </c>
+      <c r="I14" s="3">
         <v>-44400</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>38200</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>157800</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>59600</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>2400</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>1192400</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>47900</v>
       </c>
-      <c r="O14" s="3" t="s">
+      <c r="P14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>57300</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>-13600</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>-600</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>200</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>35200</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>-52600</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>-12000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>-47100</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>45800</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>175100</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>71000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>71700</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>75500</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>136500</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>185500</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>304900</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>46100</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>61800</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>33100</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>23500</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>18500</v>
-      </c>
-      <c r="AK14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AL14" s="3" t="s">
         <v>8</v>
@@ -1592,8 +1612,8 @@
       <c r="AM14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AN14" s="3">
-        <v>0</v>
+      <c r="AN14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AO14" s="3">
         <v>0</v>
@@ -1601,8 +1621,11 @@
       <c r="AP14" s="3">
         <v>0</v>
       </c>
+      <c r="AQ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1610,67 +1633,67 @@
         <v>8100</v>
       </c>
       <c r="E15" s="3">
+        <v>8100</v>
+      </c>
+      <c r="F15" s="3">
         <v>8700</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>9000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>9700</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>10100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>10900</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>11200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>11400</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>11300</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>11400</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>11300</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>13100</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>14100</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>19400</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>14500</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>14800</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>15100</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>15400</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>15600</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>16000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>15900</v>
-      </c>
-      <c r="Y15" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="Z15" s="3" t="s">
         <v>8</v>
@@ -1687,8 +1710,8 @@
       <c r="AD15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE15" s="3">
-        <v>0</v>
+      <c r="AE15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AF15" s="3">
         <v>0</v>
@@ -1723,8 +1746,11 @@
       <c r="AP15" s="3">
         <v>0</v>
       </c>
+      <c r="AQ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1764,252 +1790,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1461400</v>
+      </c>
+      <c r="E17" s="3">
         <v>1411300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1347200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1369500</v>
       </c>
-      <c r="G17" s="3">
-        <v>1284400</v>
-      </c>
       <c r="H17" s="3">
+        <v>1276400</v>
+      </c>
+      <c r="I17" s="3">
         <v>1251900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1278800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1267300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1226500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1262200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1260300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1214300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1239000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1187100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1198300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1095500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1185700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1251700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1254200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1286200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1250500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1315400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1412300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1229100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1301900</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1281900</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1428200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1445500</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1421100</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1014400</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1025500</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>1019700</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>1029300</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>1034700</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>1031300</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>982400</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>935500</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>934000</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>900500</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>895300</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>364200</v>
+      </c>
+      <c r="E18" s="3">
         <v>333200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>344800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>270900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
+        <v>239100</v>
+      </c>
+      <c r="I18" s="3">
+        <v>277300</v>
+      </c>
+      <c r="J18" s="3">
+        <v>314200</v>
+      </c>
+      <c r="K18" s="3">
+        <v>248100</v>
+      </c>
+      <c r="L18" s="3">
+        <v>256800</v>
+      </c>
+      <c r="M18" s="3">
+        <v>213100</v>
+      </c>
+      <c r="N18" s="3">
+        <v>153100</v>
+      </c>
+      <c r="O18" s="3">
+        <v>227700</v>
+      </c>
+      <c r="P18" s="3">
+        <v>203800</v>
+      </c>
+      <c r="Q18" s="3">
         <v>231100</v>
       </c>
-      <c r="H18" s="3">
-        <v>277300</v>
-      </c>
-      <c r="I18" s="3">
-        <v>314200</v>
-      </c>
-      <c r="J18" s="3">
-        <v>248100</v>
-      </c>
-      <c r="K18" s="3">
-        <v>256800</v>
-      </c>
-      <c r="L18" s="3">
-        <v>213100</v>
-      </c>
-      <c r="M18" s="3">
-        <v>153100</v>
-      </c>
-      <c r="N18" s="3">
-        <v>227700</v>
-      </c>
-      <c r="O18" s="3">
-        <v>203800</v>
-      </c>
-      <c r="P18" s="3">
-        <v>231100</v>
-      </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>245100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>350200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>344700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>377700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>509200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>463800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>470900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>344300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>217800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>268500</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>117100</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>317000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>314600</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>275100</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>18300</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>200200</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>230400</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>322100</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>331300</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>321100</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>344300</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>355300</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>318900</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>258600</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>294200</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>306300</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2052,356 +2085,363 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-140900</v>
+      </c>
+      <c r="E20" s="3">
         <v>-13700</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-10800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-69900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-84700</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>4700</v>
       </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
       <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
         <v>-30400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-17500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-42800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-37100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>6400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>16600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-26000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>162900</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-76500</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-37000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-34200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>201800</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>244600</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>203000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>157600</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>206300</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>151900</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>23100</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-103300</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>43000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>76500</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>91200</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>89700</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-53200</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>49800</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>12400</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>35700</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>78700</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>66000</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>46900</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>55300</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>40300</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>63300</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>513200</v>
+      </c>
+      <c r="E21" s="3">
         <v>355000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>364300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>349800</v>
       </c>
-      <c r="G21" s="3">
-        <v>325500</v>
-      </c>
       <c r="H21" s="3">
+        <v>333500</v>
+      </c>
+      <c r="I21" s="3">
         <v>282700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>325100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>289700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>285700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>267200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>201600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>232600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>200300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>271200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>456600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>321600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>357000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>393000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>761400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>759400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>726700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>553000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>477300</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>472000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>190500</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>262100</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>410100</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>400100</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>149800</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>326200</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>213700</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>411500</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>376100</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>390400</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>457600</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>451000</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>392000</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>340200</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>360200</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>395200</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>116100</v>
+      </c>
+      <c r="E22" s="3">
         <v>128600</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>-276100</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>120200</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>125600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>112800</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>-272500</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>131400</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>136000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>63100</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>-305300</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>135400</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>128100</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>112300</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>17600</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>18600</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>25800</v>
-      </c>
-      <c r="T22" s="3">
-        <v>23200</v>
       </c>
       <c r="U22" s="3">
         <v>23200</v>
       </c>
       <c r="V22" s="3">
+        <v>23200</v>
+      </c>
+      <c r="W22" s="3">
         <v>23100</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>24600</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>23800</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>24400</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>33800</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>34800</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>36300</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>34600</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>35000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>33000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>33100</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>29200</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>29600</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>29500</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>23200</v>
-      </c>
-      <c r="AK22" s="3">
-        <v>23600</v>
       </c>
       <c r="AL22" s="3">
         <v>23600</v>
@@ -2410,260 +2450,269 @@
         <v>23600</v>
       </c>
       <c r="AN22" s="3">
+        <v>23600</v>
+      </c>
+      <c r="AO22" s="3">
         <v>24000</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>23500</v>
       </c>
-      <c r="AP22" s="3">
+      <c r="AQ22" s="3">
         <v>23900</v>
       </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>455400</v>
+      </c>
+      <c r="E23" s="3">
         <v>300200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-1345400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>346700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>274400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>344900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>317400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>145100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>259900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>282900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-933500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>230000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>229900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>235700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>390400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>255100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>281900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>320300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>687800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>685300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>649300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>478100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>399700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>386600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>105400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>177400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>323000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>316600</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>76500</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>256800</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>148000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>342300</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>314200</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>333600</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>399400</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>397700</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>342200</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>289900</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>311000</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>345700</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>116500</v>
+      </c>
+      <c r="E24" s="3">
         <v>81100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-349500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-9700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>77000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>77600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>78700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>41500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>64000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>68700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-266400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>61300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>65500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>69900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>89600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>86800</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>63000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>82800</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>130700</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>139700</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>154200</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>106500</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>69600</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>91900</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>43400</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>57400</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>80400</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>74000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>14500</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>66200</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>40100</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>61100</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>72300</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>68400</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>107500</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>123100</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>92600</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>75700</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>92900</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>89800</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2784,252 +2833,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>338900</v>
+      </c>
+      <c r="E26" s="3">
         <v>219100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-995900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>356400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>197400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>267300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>238700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>103600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>195900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>214200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-667100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>168700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>164400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>165800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>300800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>168300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>218900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>237500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>557100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>545600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>495100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>371600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>330100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>294700</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>62000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>120000</v>
-      </c>
-      <c r="AC26" s="3">
-        <v>242600</v>
       </c>
       <c r="AD26" s="3">
         <v>242600</v>
       </c>
       <c r="AE26" s="3">
+        <v>242600</v>
+      </c>
+      <c r="AF26" s="3">
         <v>62000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>190600</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>107900</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>281200</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>241900</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>265200</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>291900</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>274600</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>249600</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>214200</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>218100</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>255900</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>345300</v>
+      </c>
+      <c r="E27" s="3">
         <v>230400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-1186200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>301300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-12500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>171100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>209300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>55000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>132200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>141500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-742300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>131400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>132200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>145000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>187800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>177400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>121000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>197700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>426800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>330100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>368300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>267800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>210400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>191700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>40500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>81500</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>179800</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>167100</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>40100</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>171700</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>123700</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>261300</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>237600</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>246400</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>265400</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>259500</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>232400</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>212000</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>226500</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>241200</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3150,8 +3208,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3200,8 +3261,8 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-      <c r="S29" s="3" t="s">
-        <v>8</v>
+      <c r="S29" s="3">
+        <v>0</v>
       </c>
       <c r="T29" s="3" t="s">
         <v>8</v>
@@ -3218,11 +3279,11 @@
       <c r="X29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Y29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z29" s="3">
         <v>700</v>
-      </c>
-      <c r="Z29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AA29" s="3" t="s">
         <v>8</v>
@@ -3242,11 +3303,11 @@
       <c r="AF29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AG29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH29" s="3">
         <v>-13100</v>
-      </c>
-      <c r="AH29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AI29" s="3" t="s">
         <v>8</v>
@@ -3254,11 +3315,11 @@
       <c r="AJ29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AK29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL29" s="3">
         <v>130700</v>
-      </c>
-      <c r="AL29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AM29" s="3" t="s">
         <v>8</v>
@@ -3266,14 +3327,17 @@
       <c r="AN29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AO29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AP29" s="3" t="s">
+      <c r="AO29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AP29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3394,8 +3458,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3516,252 +3583,261 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>140900</v>
+      </c>
+      <c r="E32" s="3">
         <v>13700</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>10800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>69900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>84700</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-4700</v>
       </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
       <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
         <v>30400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>17500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>42800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>37100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-6400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-16600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>26000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-162900</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>76500</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>37000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>34200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-201800</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-244600</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-203000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-157600</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-206300</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-151900</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-23100</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>103300</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-43000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-76500</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-91200</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-89700</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>53200</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-49800</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-12400</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-35700</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-78700</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-66000</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-46900</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-55300</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>-40300</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>-63300</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>382300</v>
+      </c>
+      <c r="E33" s="3">
         <v>268600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-1061100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>345700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>203400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>230300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>268500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>114200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>191400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>200700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-683100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>190600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>191400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>204200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>187800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>177400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>121000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>197700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>426800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>330100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>368300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>267800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>211100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>191700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>40500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>81500</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>179800</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>167100</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>40100</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>171700</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>110600</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>261300</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>237600</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>246400</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>396100</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>259500</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>232400</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>212000</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>226500</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>241200</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3882,257 +3958,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>382300</v>
+      </c>
+      <c r="E35" s="3">
         <v>268600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-1061100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>345700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>203400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>230300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>268500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>114200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>191400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>200700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-683100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>190600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>191400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>204200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>187800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>177400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>121000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>197700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>426800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>330100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>368300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>267800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>211100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>191700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>40500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>81500</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>179800</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>167100</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>40100</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>171700</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>110600</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>261300</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>237600</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>246400</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>396100</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>259500</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>232400</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>212000</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>226500</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>241200</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4175,8 +4260,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4219,130 +4305,134 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>915400</v>
+      </c>
+      <c r="E41" s="3">
         <v>806900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1037500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>973100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>922700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>821700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>986500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1044900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>878500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>895700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1469200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1241500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1009900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>889000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1234700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1023600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>936800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1309600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1896400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1773200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1333000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1158300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1408400</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1066600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>987100</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>940500</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1049000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1048600</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1199400</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1017100</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>1147700</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>1631500</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>1480500</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>1861500</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>2006400</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>1716300</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>1646100</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>1397000</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>1328000</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>1581300</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4380,14 +4470,14 @@
         <v>0</v>
       </c>
       <c r="O42" s="3">
+        <v>0</v>
+      </c>
+      <c r="P42" s="3">
         <v>15100</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>25900</v>
       </c>
-      <c r="Q42" s="3">
-        <v>0</v>
-      </c>
       <c r="R42" s="3">
         <v>0</v>
       </c>
@@ -4463,130 +4553,136 @@
       <c r="AP42" s="3">
         <v>0</v>
       </c>
+      <c r="AQ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>805500</v>
+      </c>
+      <c r="E43" s="3">
         <v>911100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>884700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>810500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>747100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>794600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>740800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>710800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>677100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>708300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>701500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>645400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>703200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>805700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>801800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>701200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>747400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>756300</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>877800</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>957700</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1023600</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1118700</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>850500</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>979600</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>830200</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>914500</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>1018300</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>1024900</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>974000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>1073300</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>795300</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>1409100</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>1535500</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>1432600</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>1416300</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>1378900</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>1551200</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>1475700</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>1217100</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>1200000</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4629,8 +4725,8 @@
       <c r="P44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -4707,8 +4803,11 @@
       <c r="AP44" s="3">
         <v>0</v>
       </c>
+      <c r="AQ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4736,146 +4835,149 @@
       <c r="K45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M45" s="3">
         <v>9649300</v>
-      </c>
-      <c r="M45" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="N45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O45" s="3">
+      <c r="O45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P45" s="3">
         <v>9530100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>9770000</v>
       </c>
-      <c r="Q45" s="3">
-        <v>0</v>
-      </c>
       <c r="R45" s="3">
         <v>0</v>
       </c>
       <c r="S45" s="3">
         <v>0</v>
       </c>
-      <c r="T45" s="3" t="s">
+      <c r="T45" s="3">
+        <v>0</v>
+      </c>
+      <c r="U45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>166000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>144800</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>139600</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>132500</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>149200</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>132200</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>128600</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>124500</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>144000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>137200</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>139200</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>116800</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>127100</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>130900</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>122200</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>124900</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>124400</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>122800</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>118300</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>118000</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>116900</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>130800</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1720900</v>
+      </c>
+      <c r="E46" s="3">
         <v>1718000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1922200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1783600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1669800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1616300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1727300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1755700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1555600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>11253300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2170700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1886900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>11258300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>11490600</v>
       </c>
-      <c r="Q46" s="3">
-        <v>0</v>
-      </c>
       <c r="R46" s="3">
         <v>0</v>
       </c>
@@ -4951,374 +5053,386 @@
       <c r="AP46" s="3">
         <v>0</v>
       </c>
+      <c r="AQ46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1317900</v>
+      </c>
+      <c r="E47" s="3">
         <v>1198400</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1252900</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1038700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1006400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>963700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1020400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>904000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>765800</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>752300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>722400</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>753000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>791200</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>791700</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>9528000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>9403800</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>9604600</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>10011400</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>9968800</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>9830600</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>9270000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>8769700</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>8736800</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>8488200</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>8107600</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>8308400</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>8637500</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>7888700</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>7499800</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>7369000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>6827000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>6718400</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>732800</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>713600</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>674600</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>690900</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>642600</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>689300</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>795300</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>877700</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>370200</v>
+      </c>
+      <c r="E48" s="3">
         <v>364900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>676100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>387700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>453600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>458400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>479000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>580300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>574400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>583600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>599500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>586200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>585300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>572600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>561100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>504000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>491400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>499600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>518100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>512500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>524800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>555900</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>839500</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>858500</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>879600</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>875200</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>908500</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>883000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>902000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>665500</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>468700</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>469200</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>475700</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>484400</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>490700</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>483000</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>482200</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>467900</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>464700</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>444600</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>12306000</v>
+      </c>
+      <c r="E49" s="3">
         <v>12331600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>12404400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>14191000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>14334600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>14119600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>14067400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>14547100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>14424700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>14453400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>14539600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>15668900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>15793000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>15733900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>15698900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>15551800</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>15820600</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>16053600</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>16110500</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>16124800</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>16229000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>16214900</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>16221900</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>16044700</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>15931400</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>15869200</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>15867700</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>15670000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>15766600</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>9379100</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>9333200</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>9468000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>9466000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>8163600</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>8149400</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>8134600</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>7666500</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>7568700</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>7528600</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>7650500</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5439,8 +5553,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5561,53 +5678,56 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>11758100</v>
+      </c>
+      <c r="E52" s="3">
         <v>11221700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>10838400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>11037900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>11032500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>10985600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>9714800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>9715500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>9847100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1034600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>10901600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>10536500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1030000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1144500</v>
       </c>
-      <c r="Q52" s="3">
-        <v>0</v>
-      </c>
       <c r="R52" s="3">
         <v>0</v>
       </c>
@@ -5683,8 +5803,11 @@
       <c r="AP52" s="3">
         <v>0</v>
       </c>
+      <c r="AQ52" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5805,130 +5928,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>27473100</v>
+      </c>
+      <c r="E54" s="3">
         <v>26834600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>27094000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>28438900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>28496900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>28143600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>27008900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>27502600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>27167600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>28077200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>28933800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>29431500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>29457800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>29733300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>29756800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>29271900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>30186700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>31853800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>32685600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>32813900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>33248400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>34881500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>36504100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>36037500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>35579100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>37010700</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>39420300</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>37891400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>38501400</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>32206600</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>30978400</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>32503800</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>32459100</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>31619100</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>31668800</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>30372500</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>28248500</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>26598900</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>25734300</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>24137700</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5971,8 +6100,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -6015,130 +6145,134 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1618400</v>
+      </c>
+      <c r="E57" s="3">
         <v>1510800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>20400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1496200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1431800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1415700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>30600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1455600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1362900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1321200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>31500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1291600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1360700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1465800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1314800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1332400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1352900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1271300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1065300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1401700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1485000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1930800</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1601200</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1475800</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1522000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1580400</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1539200</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>1525100</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>1570900</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>1000800</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>1087200</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>864200</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>819700</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>820800</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>895700</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>901900</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>788300</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>766700</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>812400</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>868300</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -6146,20 +6280,20 @@
         <v>0</v>
       </c>
       <c r="E58" s="3">
+        <v>0</v>
+      </c>
+      <c r="F58" s="3">
         <v>566500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>499800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>499600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>499400</v>
       </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
       <c r="J58" s="3">
         <v>0</v>
       </c>
@@ -6170,11 +6304,11 @@
         <v>0</v>
       </c>
       <c r="M58" s="3">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3">
         <v>599900</v>
       </c>
-      <c r="N58" s="3">
-        <v>0</v>
-      </c>
       <c r="O58" s="3">
         <v>0</v>
       </c>
@@ -6259,19 +6393,22 @@
       <c r="AP58" s="3">
         <v>0</v>
       </c>
+      <c r="AQ58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E59" s="3">
+      <c r="E59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F59" s="3">
         <v>100100</v>
-      </c>
-      <c r="F59" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="G59" s="3" t="s">
         <v>8</v>
@@ -6279,11 +6416,11 @@
       <c r="H59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I59" s="3">
+      <c r="I59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J59" s="3">
         <v>146000</v>
-      </c>
-      <c r="J59" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="K59" s="3" t="s">
         <v>8</v>
@@ -6291,11 +6428,11 @@
       <c r="L59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M59" s="3">
+      <c r="M59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N59" s="3">
         <v>110500</v>
-      </c>
-      <c r="N59" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="O59" s="3" t="s">
         <v>8</v>
@@ -6303,131 +6440,134 @@
       <c r="P59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="Q59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R59" s="3">
         <v>1529500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1434700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1625700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>2157500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>3047700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>3372600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>4444500</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>6568900</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>8973400</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>9236700</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>9071400</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>10167500</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>12385300</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>11944900</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>12859800</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>13138700</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>12210000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>13642400</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>13580000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>14085300</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>13924400</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>13521900</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>12193900</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>10543600</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>9537800</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>8555800</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2429200</v>
+      </c>
+      <c r="E60" s="3">
         <v>2089600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2443700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2889000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2647800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2458000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1790200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2342100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1952600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1773700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2603700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2025200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1931300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1900500</v>
       </c>
-      <c r="Q60" s="3">
-        <v>0</v>
-      </c>
       <c r="R60" s="3">
         <v>0</v>
       </c>
@@ -6503,252 +6643,261 @@
       <c r="AP60" s="3">
         <v>0</v>
       </c>
+      <c r="AQ60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1624000</v>
+      </c>
+      <c r="E61" s="3">
         <v>1966700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1665300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1124800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1384300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>465400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1345500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>890300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>890100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1257500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1323300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1489100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1488600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1488100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>8078000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>8035800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>8402300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>9170100</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>9421200</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>9309000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>8834500</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>8784100</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>8796700</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>8698700</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>8654600</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>8761500</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>8314900</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>7780900</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>7270100</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>7727400</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>7634800</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>7635100</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>7970400</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>6579100</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>6875600</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>6398900</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>6004300</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>6366500</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>6505500</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>5933200</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>9007700</v>
+      </c>
+      <c r="E62" s="3">
         <v>8573600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>9078600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>8314000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>8192500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>8104400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>6922500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>7046700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>7202900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>7829500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>7765100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>7712200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>7685800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>7843600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1662700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1678800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1675200</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1704500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1626300</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1591100</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1575300</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1566300</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1523500</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>1527100</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>1507400</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>1500800</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>1529500</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>1523100</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>1538800</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>367600</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>326400</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>304300</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>303500</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>313400</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>275500</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>351500</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>366500</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>390300</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>309700</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>341000</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6869,8 +7018,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6991,8 +7143,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7113,130 +7268,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>14002900</v>
+      </c>
+      <c r="E66" s="3">
         <v>13572300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>14089100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>13646600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>13538000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>12356200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>11340100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>11596000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>11402200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>12224400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>13017800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>12839800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>12749200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>12923500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>14543200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>14368200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>15073000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>16508800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>17189800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>17733800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>18340400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>20333700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>22142300</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>22103500</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>21977100</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>23511400</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>25557800</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>24318200</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>24566700</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>23537300</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>22399600</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>23516700</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>23641800</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>22723800</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>22972700</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>22058500</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>20276000</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>18935600</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>18230500</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>16401000</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7279,8 +7440,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7401,8 +7563,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7523,8 +7688,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7535,13 +7703,13 @@
         <v>2510500</v>
       </c>
       <c r="F70" s="3">
-        <v>3010500</v>
+        <v>2510500</v>
       </c>
       <c r="G70" s="3">
         <v>3010500</v>
       </c>
       <c r="H70" s="3">
-        <v>4010500</v>
+        <v>3010500</v>
       </c>
       <c r="I70" s="3">
         <v>4010500</v>
@@ -7613,7 +7781,7 @@
         <v>4010500</v>
       </c>
       <c r="AF70" s="3">
-        <v>0</v>
+        <v>4010500</v>
       </c>
       <c r="AG70" s="3">
         <v>0</v>
@@ -7645,8 +7813,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7767,130 +7938,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>6270400</v>
+      </c>
+      <c r="E72" s="3">
         <v>6021900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>5886800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>7167600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>6961300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>7069000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>6990400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>6874000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>6917000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>6878000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>6826700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>7658800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>7617900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>7577600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>7518300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>7416200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>7323200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>7287900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>7169200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>6821200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>6570100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>6279900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>6085000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>5944500</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>5825000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>5856600</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>5917800</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>5880000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>5856800</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>5942100</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>5884500</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>5892600</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>5747300</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>5626600</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>5489100</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>5199800</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>5051300</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>4930600</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>4833400</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>4721000</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -8011,8 +8188,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8133,8 +8313,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8255,130 +8438,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>9961400</v>
+      </c>
+      <c r="E76" s="3">
         <v>9744500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>9720500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>10995100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>10862600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>10688200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>10549400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>10743800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>10574500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>10544300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>10587100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>11243400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>11318400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>11332500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>11203100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>10893200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>11103200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>11334500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>11485300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>11069600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>10897500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>10537300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>10351300</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>9923500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>9591500</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>9488800</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>9852000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>9562700</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>9924200</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>8669300</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>8578800</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>8987100</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>8817300</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>8895300</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>8696100</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>8314000</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>7972500</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>7663300</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>7503800</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>7736700</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8499,257 +8688,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>382300</v>
+      </c>
+      <c r="E81" s="3">
         <v>268600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-1061100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>345700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>203400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>230300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>268500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>114200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>191400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>200700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-683100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>190600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>191400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>204200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>187800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>177400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>121000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>197700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>426800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>330100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>368300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>267800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>211100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>191700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>40500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>81500</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>179800</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>167100</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>40100</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>171700</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>110600</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>261300</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>237600</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>246400</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>396100</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>259500</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>232400</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>212000</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>226500</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>241200</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8792,130 +8990,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>30400</v>
+      </c>
+      <c r="E83" s="3">
         <v>31400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>33200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>32800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>35000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>33800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>35000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>30900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>34300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>32700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>29200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>33400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>34500</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>34400</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>48600</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>47900</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>49300</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>49500</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>50400</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>51000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>52800</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>51100</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>53200</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>51600</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>50300</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>48400</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>52500</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>48500</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>40300</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>36300</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>36500</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>39600</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>32400</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>33600</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>34600</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>29700</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>26200</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>26300</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>25700</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>25600</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9036,8 +9238,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9158,8 +9363,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9280,8 +9488,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9402,8 +9613,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9524,130 +9738,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>734200</v>
+      </c>
+      <c r="E89" s="3">
         <v>212600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>455800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>606200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>547900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-84600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>316900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>438400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>489100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-54400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>714300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>354100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>331300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-98900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>463500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>492000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>123100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-375400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>5000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>601000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>507700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-35600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>564000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>401700</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>347400</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-77300</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>447300</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>322100</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>460100</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-120300</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>166800</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>166900</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>449000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-91500</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>358700</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>230400</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>465700</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>315900</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>-412800</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>367500</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9690,130 +9910,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-30500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-14200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-23600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-19800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-17500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-23400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>7000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-28400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-26700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-21000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-40300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-39200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-46700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-38100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-73100</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-62700</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-33200</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-23900</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-35600</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-26000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-26900</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-20300</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-41400</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-73400</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>19000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-19200</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-48700</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-26600</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-27900</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-21100</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-34200</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-22100</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-25600</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-20600</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-29000</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-22800</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-32800</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-54200</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-46400</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-36000</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9934,8 +10158,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10056,130 +10283,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-705500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-733200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-352200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-254800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-275400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-92000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-16900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>27900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>344700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-287300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-261600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>66500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-94700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>45500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-137600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-82200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-76700</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-79100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-268500</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-364400</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-83800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-131200</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-36100</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-86000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-291000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-452000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-656100</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-235000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-200900</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-333400</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-215800</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-865400</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-1519700</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-297800</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-471100</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-558300</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>105900</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-37600</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-238800</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-269000</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10222,130 +10455,134 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>96800</v>
+      </c>
+      <c r="E96" s="3">
         <v>95300</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>94600</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>95000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>95200</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>92500</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>92800</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>95300</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>93200</v>
-      </c>
-      <c r="L96" s="3">
-        <v>90200</v>
       </c>
       <c r="M96" s="3">
         <v>90200</v>
       </c>
       <c r="N96" s="3">
+        <v>90200</v>
+      </c>
+      <c r="O96" s="3">
         <v>90100</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>91900</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>85700</v>
-      </c>
-      <c r="Q96" s="3">
-        <v>-85700</v>
       </c>
       <c r="R96" s="3">
         <v>-85700</v>
       </c>
       <c r="S96" s="3">
+        <v>-85700</v>
+      </c>
+      <c r="T96" s="3">
         <v>-85600</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-77800</v>
-      </c>
-      <c r="U96" s="3">
-        <v>-78800</v>
       </c>
       <c r="V96" s="3">
         <v>-78800</v>
       </c>
       <c r="W96" s="3">
+        <v>-78800</v>
+      </c>
+      <c r="X96" s="3">
         <v>-78600</v>
-      </c>
-      <c r="X96" s="3">
-        <v>-71500</v>
       </c>
       <c r="Y96" s="3">
         <v>-71500</v>
       </c>
       <c r="Z96" s="3">
+        <v>-71500</v>
+      </c>
+      <c r="AA96" s="3">
         <v>-71400</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-73600</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-140900</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-157100</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-126500</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-125400</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-120100</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-122300</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-124300</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-124400</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-119600</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-118900</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-119000</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
         <v>-118900</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-114800</v>
       </c>
-      <c r="AO96" s="3">
+      <c r="AP96" s="3">
         <v>-114100</v>
       </c>
-      <c r="AP96" s="3">
+      <c r="AQ96" s="3">
         <v>-115700</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10466,8 +10703,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10588,8 +10828,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10710,370 +10953,382 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-120600</v>
+      </c>
+      <c r="E100" s="3">
         <v>271300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>356100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-310100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-724800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>529300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-392500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-409100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-711700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-148300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-110300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-125500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-171100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-178500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-168100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-265800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-477700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-55300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>103100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>359100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-482700</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>137800</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-55600</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-301600</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-25000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>96300</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>325200</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>52100</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-89000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-87000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-44100</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>789200</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>839500</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-44600</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>389800</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>367100</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-364200</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-223700</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>453600</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>53700</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>70800</v>
+      </c>
+      <c r="E101" s="3">
         <v>24700</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-50900</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>40900</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-6300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-16100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>34100</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-27100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>6700</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>12700</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>50300</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-50800</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-50000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-23200</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>50300</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-50800</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-50000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-23200</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-2000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-23300</v>
       </c>
-      <c r="W101" s="3">
-        <v>0</v>
-      </c>
       <c r="X101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y101" s="3">
         <v>-14400</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>46400</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>35300</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>10300</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-38700</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>34200</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-23900</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-3200</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>3600</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-15800</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-10300</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-57200</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>38500</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>17000</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>31000</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>41700</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>14400</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>-55300</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>-17100</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-95800</v>
+      </c>
+      <c r="E102" s="3">
         <v>-273700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>456000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>31900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-381500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>377400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-143400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>98100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>115800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-506100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>376500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>268000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>72200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-219200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>208100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>93200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-481300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-533000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-162400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>572400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-58800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-43400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>518700</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>49400</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>41700</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-471700</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>166900</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>99000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>167000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-537100</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-108900</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>80400</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-288400</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-395400</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>290100</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>70200</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>249100</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>69000</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>-253300</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>135100</v>
       </c>
     </row>
